--- a/data/trans_dic/P43E-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P43E-Estudios-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,48</t>
+          <t>10,1; 15,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,44</t>
+          <t>3,19; 7,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,58</t>
+          <t>4,43; 8,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,48</t>
+          <t>10,1; 15,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,44</t>
+          <t>3,19; 7,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,58</t>
+          <t>4,43; 8,4</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 25,86</t>
+          <t>20,79; 25,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 16,14</t>
+          <t>12,18; 16,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 21,63</t>
+          <t>19,16; 23,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 25,86</t>
+          <t>20,79; 25,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 16,14</t>
+          <t>12,18; 16,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 21,63</t>
+          <t>19,16; 23,61</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 49,53</t>
+          <t>37,38; 49,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,17; 40,68</t>
+          <t>31,3; 41,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,39; 52,76</t>
+          <t>42,28; 51,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 49,53</t>
+          <t>37,38; 49,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,17; 40,68</t>
+          <t>31,3; 41,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,39; 52,76</t>
+          <t>42,28; 51,35</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 25,16</t>
+          <t>21,17; 24,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,72; 17,86</t>
+          <t>14,72; 17,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,97; 25,02</t>
+          <t>22,74; 26,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 25,16</t>
+          <t>21,17; 24,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,72; 17,86</t>
+          <t>14,72; 17,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,97; 25,02</t>
+          <t>22,74; 26,33</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>18819</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69499; 106642</t>
+          <t>69597; 105566</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15094; 35364</t>
+          <t>15182; 35856</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12365; 24523</t>
+          <t>13459; 25525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69499; 106642</t>
+          <t>69597; 105566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15094; 35364</t>
+          <t>15182; 35856</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12365; 24523</t>
+          <t>13459; 25525</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175091</t>
+          <t>194444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>175091</t>
+          <t>194444</t>
         </is>
       </c>
     </row>
@@ -1217,32 +1217,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>253294; 313779</t>
+          <t>252278; 313106</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>152615; 202691</t>
+          <t>152966; 202652</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134069; 202240</t>
+          <t>175267; 216028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>253294; 313779</t>
+          <t>252278; 313106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>152615; 202691</t>
+          <t>152966; 202652</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>134069; 202240</t>
+          <t>175267; 216028</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165765</t>
+          <t>180579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>165765</t>
+          <t>180579</t>
         </is>
       </c>
     </row>
@@ -1335,32 +1335,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>128253; 170404</t>
+          <t>128582; 168737</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128739; 167989</t>
+          <t>129254; 170056</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>150439; 182905</t>
+          <t>163538; 198622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128253; 170404</t>
+          <t>128582; 168737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>128739; 167989</t>
+          <t>129254; 170056</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>150439; 182905</t>
+          <t>163538; 198622</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358672</t>
+          <t>393843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>358672</t>
+          <t>393843</t>
         </is>
       </c>
     </row>
@@ -1453,32 +1453,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>476533; 565096</t>
+          <t>475469; 557737</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>315608; 382920</t>
+          <t>315699; 384152</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>297269; 392207</t>
+          <t>365038; 422719</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>476533; 565096</t>
+          <t>475469; 557737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>315608; 382920</t>
+          <t>315699; 384152</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>297269; 392207</t>
+          <t>365038; 422719</t>
         </is>
       </c>
     </row>
